--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/128.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/128.xlsx
@@ -426,13 +426,13 @@
         <v>-19.19667099451689</v>
       </c>
       <c r="E2">
-        <v>-20.9683356571179</v>
+        <v>-14.90045672375408</v>
       </c>
       <c r="F2">
-        <v>-4.89443959628229</v>
+        <v>-4.916928942900894</v>
       </c>
       <c r="G2">
-        <v>-13.44759272682824</v>
+        <v>-10.62826593467411</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.55427835218644</v>
       </c>
       <c r="E3">
-        <v>-21.45865618029841</v>
+        <v>-16.31424178047476</v>
       </c>
       <c r="F3">
-        <v>-4.885549557315446</v>
+        <v>-4.979078864030733</v>
       </c>
       <c r="G3">
-        <v>-14.35785370721517</v>
+        <v>-10.49527138872497</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.79955922085546</v>
       </c>
       <c r="E4">
-        <v>-21.45301823015885</v>
+        <v>-16.11823131152676</v>
       </c>
       <c r="F4">
-        <v>-4.769871362984106</v>
+        <v>-4.735539675975081</v>
       </c>
       <c r="G4">
-        <v>-13.74880602326437</v>
+        <v>-10.2979198374924</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.9880755263705</v>
       </c>
       <c r="E5">
-        <v>-22.51412573116216</v>
+        <v>-17.10788402116304</v>
       </c>
       <c r="F5">
-        <v>-5.131978919239465</v>
+        <v>-5.177287302702987</v>
       </c>
       <c r="G5">
-        <v>-13.25546852700218</v>
+        <v>-9.591230923406336</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.09528933832864</v>
       </c>
       <c r="E6">
-        <v>-23.55382713553122</v>
+        <v>-17.27337710377335</v>
       </c>
       <c r="F6">
-        <v>-5.119677663307892</v>
+        <v>-5.000092059937548</v>
       </c>
       <c r="G6">
-        <v>-12.86140104928057</v>
+        <v>-9.380097571093776</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.13581112237315</v>
       </c>
       <c r="E7">
-        <v>-23.21629732536951</v>
+        <v>-18.01085268134449</v>
       </c>
       <c r="F7">
-        <v>-5.488473457973455</v>
+        <v>-5.07995247613924</v>
       </c>
       <c r="G7">
-        <v>-12.92834690117571</v>
+        <v>-9.024511874720657</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.09251531174261</v>
       </c>
       <c r="E8">
-        <v>-23.89210414390419</v>
+        <v>-19.11450519564987</v>
       </c>
       <c r="F8">
-        <v>-5.513369211897191</v>
+        <v>-5.100557286916475</v>
       </c>
       <c r="G8">
-        <v>-12.34707800484494</v>
+        <v>-8.057567733610329</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.98340028672881</v>
       </c>
       <c r="E9">
-        <v>-23.67282637550478</v>
+        <v>-19.63779300960621</v>
       </c>
       <c r="F9">
-        <v>-5.943206572107647</v>
+        <v>-5.478816350791618</v>
       </c>
       <c r="G9">
-        <v>-11.91523058142917</v>
+        <v>-8.368368369928188</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.80994721606384</v>
       </c>
       <c r="E10">
-        <v>-24.36702785545862</v>
+        <v>-19.97021470108727</v>
       </c>
       <c r="F10">
-        <v>-5.48679435724798</v>
+        <v>-5.349768306579095</v>
       </c>
       <c r="G10">
-        <v>-11.41837066471319</v>
+        <v>-7.54554882887003</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.58725352634564</v>
       </c>
       <c r="E11">
-        <v>-25.73054685069416</v>
+        <v>-20.95265355162933</v>
       </c>
       <c r="F11">
-        <v>-5.557649591413838</v>
+        <v>-5.206427611198668</v>
       </c>
       <c r="G11">
-        <v>-10.78733764783609</v>
+        <v>-6.950173697996421</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.352530675214744</v>
       </c>
       <c r="E12">
-        <v>-27.51781780119745</v>
+        <v>-21.33465297654637</v>
       </c>
       <c r="F12">
-        <v>-5.422331634329526</v>
+        <v>-5.413286690658357</v>
       </c>
       <c r="G12">
-        <v>-10.00942565701815</v>
+        <v>-6.845782265506583</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.136031500610796</v>
       </c>
       <c r="E13">
-        <v>-28.28461977644226</v>
+        <v>-21.80234018663654</v>
       </c>
       <c r="F13">
-        <v>-5.275578893616968</v>
+        <v>-5.277182612908788</v>
       </c>
       <c r="G13">
-        <v>-8.588178662099176</v>
+        <v>-6.12977747627301</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.001467720803234</v>
       </c>
       <c r="E14">
-        <v>-27.04799767984967</v>
+        <v>-23.08083255390406</v>
       </c>
       <c r="F14">
-        <v>-6.152176331709669</v>
+        <v>-5.351604797111101</v>
       </c>
       <c r="G14">
-        <v>-8.958019567564396</v>
+        <v>-5.621813989818318</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.011309961602049</v>
       </c>
       <c r="E15">
-        <v>-28.72457008323545</v>
+        <v>-23.18197149239137</v>
       </c>
       <c r="F15">
-        <v>-5.37872637424616</v>
+        <v>-4.991169714641994</v>
       </c>
       <c r="G15">
-        <v>-8.776876447292095</v>
+        <v>-4.990648551119649</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.218454601415604</v>
       </c>
       <c r="E16">
-        <v>-29.20196181312406</v>
+        <v>-24.4364448335222</v>
       </c>
       <c r="F16">
-        <v>-5.390473452385259</v>
+        <v>-4.672969772572023</v>
       </c>
       <c r="G16">
-        <v>-8.033754979546352</v>
+        <v>-4.445044161883443</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.682207002666668</v>
       </c>
       <c r="E17">
-        <v>-30.6856257522571</v>
+        <v>-24.54599314824176</v>
       </c>
       <c r="F17">
-        <v>-5.423385317665886</v>
+        <v>-4.849227303437493</v>
       </c>
       <c r="G17">
-        <v>-7.535084194420394</v>
+        <v>-4.636377141325621</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.423369953713686</v>
       </c>
       <c r="E18">
-        <v>-30.15690603372855</v>
+        <v>-25.68313372783385</v>
       </c>
       <c r="F18">
-        <v>-5.628566953134907</v>
+        <v>-4.194269504372634</v>
       </c>
       <c r="G18">
-        <v>-7.860762422391736</v>
+        <v>-4.433175856125155</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.443486838530132</v>
       </c>
       <c r="E19">
-        <v>-30.09186809003039</v>
+        <v>-25.97739849732628</v>
       </c>
       <c r="F19">
-        <v>-4.610357622431422</v>
+        <v>-4.247024082419919</v>
       </c>
       <c r="G19">
-        <v>-7.110864267927105</v>
+        <v>-4.505819156893383</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.722592706826499</v>
       </c>
       <c r="E20">
-        <v>-30.72102483357506</v>
+        <v>-26.9168938288536</v>
       </c>
       <c r="F20">
-        <v>-4.668868525560763</v>
+        <v>-4.112726673975856</v>
       </c>
       <c r="G20">
-        <v>-7.613782482979948</v>
+        <v>-4.565021642772169</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.204552934772942</v>
       </c>
       <c r="E21">
-        <v>-31.60724040416514</v>
+        <v>-27.27098879693537</v>
       </c>
       <c r="F21">
-        <v>-4.705353139449664</v>
+        <v>-3.331684729265688</v>
       </c>
       <c r="G21">
-        <v>-7.838571835642001</v>
+        <v>-4.504226784488994</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.835240193826037</v>
       </c>
       <c r="E22">
-        <v>-31.36411342740433</v>
+        <v>-27.9570933653635</v>
       </c>
       <c r="F22">
-        <v>-4.529759130873836</v>
+        <v>-3.661571278654355</v>
       </c>
       <c r="G22">
-        <v>-7.045447888071107</v>
+        <v>-5.32841027030933</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.543224001055297</v>
       </c>
       <c r="E23">
-        <v>-32.81826077295537</v>
+        <v>-27.58401503424157</v>
       </c>
       <c r="F23">
-        <v>-4.20127832096772</v>
+        <v>-3.222181185554816</v>
       </c>
       <c r="G23">
-        <v>-7.112354013419777</v>
+        <v>-4.477414676166436</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.254557130508783</v>
       </c>
       <c r="E24">
-        <v>-33.78036903944</v>
+        <v>-28.27824821351347</v>
       </c>
       <c r="F24">
-        <v>-4.349116222977945</v>
+        <v>-2.990539010138171</v>
       </c>
       <c r="G24">
-        <v>-7.007826848562829</v>
+        <v>-4.773599253928412</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.913180960749007</v>
       </c>
       <c r="E25">
-        <v>-32.641516696673</v>
+        <v>-28.59889134410058</v>
       </c>
       <c r="F25">
-        <v>-3.659176468492862</v>
+        <v>-3.146405449016329</v>
       </c>
       <c r="G25">
-        <v>-9.093020304110336</v>
+        <v>-5.463659297770715</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.463477295592817</v>
       </c>
       <c r="E26">
-        <v>-33.43291281425348</v>
+        <v>-29.37423854979787</v>
       </c>
       <c r="F26">
-        <v>-4.172365813507809</v>
+        <v>-2.883333357602665</v>
       </c>
       <c r="G26">
-        <v>-7.151663431153083</v>
+        <v>-6.075709646525634</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.875581465813973</v>
       </c>
       <c r="E27">
-        <v>-33.59978934567313</v>
+        <v>-28.19882330789294</v>
       </c>
       <c r="F27">
-        <v>-4.239325235778301</v>
+        <v>-2.505562202127769</v>
       </c>
       <c r="G27">
-        <v>-9.168573574407583</v>
+        <v>-6.041511711104962</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.135410170472582</v>
       </c>
       <c r="E28">
-        <v>-32.76097784099534</v>
+        <v>-27.49593168631838</v>
       </c>
       <c r="F28">
-        <v>-3.914255642836914</v>
+        <v>-2.84717926230748</v>
       </c>
       <c r="G28">
-        <v>-9.286150909780337</v>
+        <v>-6.206933050611265</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.240353260576144</v>
       </c>
       <c r="E29">
-        <v>-32.70748977025375</v>
+        <v>-27.89518912567864</v>
       </c>
       <c r="F29">
-        <v>-4.352915944254586</v>
+        <v>-2.856883586431276</v>
       </c>
       <c r="G29">
-        <v>-8.271078057620086</v>
+        <v>-5.68798517405727</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.210504507197829</v>
       </c>
       <c r="E30">
-        <v>-32.76177032394669</v>
+        <v>-28.66485762497031</v>
       </c>
       <c r="F30">
-        <v>-3.773269167615243</v>
+        <v>-3.083961457458496</v>
       </c>
       <c r="G30">
-        <v>-9.030563551966445</v>
+        <v>-6.14368176753795</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.067217449992425</v>
       </c>
       <c r="E31">
-        <v>-32.6315382041971</v>
+        <v>-28.05908365696425</v>
       </c>
       <c r="F31">
-        <v>-3.812067411660164</v>
+        <v>-2.540867220835084</v>
       </c>
       <c r="G31">
-        <v>-7.651406833033765</v>
+        <v>-6.586804909060477</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.838586401518267</v>
       </c>
       <c r="E32">
-        <v>-31.37328132303286</v>
+        <v>-27.61205987377108</v>
       </c>
       <c r="F32">
-        <v>-3.525877242769171</v>
+        <v>-2.76719210589316</v>
       </c>
       <c r="G32">
-        <v>-9.169278720607448</v>
+        <v>-6.684922857753396</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.555687245802135</v>
       </c>
       <c r="E33">
-        <v>-32.03092443232278</v>
+        <v>-28.17568733418775</v>
       </c>
       <c r="F33">
-        <v>-4.198530626292634</v>
+        <v>-2.74592294445888</v>
       </c>
       <c r="G33">
-        <v>-7.842676912110697</v>
+        <v>-5.801877872244817</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.23737248846678</v>
       </c>
       <c r="E34">
-        <v>-32.19223320495</v>
+        <v>-27.16358697889545</v>
       </c>
       <c r="F34">
-        <v>-3.640514179275192</v>
+        <v>-3.068445307636659</v>
       </c>
       <c r="G34">
-        <v>-7.995931996760179</v>
+        <v>-5.969245812528211</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.905811328134353</v>
       </c>
       <c r="E35">
-        <v>-30.51896205911581</v>
+        <v>-27.48471012772737</v>
       </c>
       <c r="F35">
-        <v>-3.509017481019993</v>
+        <v>-2.974291411899662</v>
       </c>
       <c r="G35">
-        <v>-8.747558255996308</v>
+        <v>-5.153106952368304</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.570261863250272</v>
       </c>
       <c r="E36">
-        <v>-31.75387692100751</v>
+        <v>-25.74154651405879</v>
       </c>
       <c r="F36">
-        <v>-3.615271339409682</v>
+        <v>-2.76985530709316</v>
       </c>
       <c r="G36">
-        <v>-8.48668064641066</v>
+        <v>-6.131247358492447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.234529394878352</v>
       </c>
       <c r="E37">
-        <v>-29.82800296655146</v>
+        <v>-26.03721511049359</v>
       </c>
       <c r="F37">
-        <v>-3.991461141512633</v>
+        <v>-2.691246554037098</v>
       </c>
       <c r="G37">
-        <v>-8.220665070148064</v>
+        <v>-5.933193971605548</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.905011429358724</v>
       </c>
       <c r="E38">
-        <v>-30.60530873725706</v>
+        <v>-25.39553487208071</v>
       </c>
       <c r="F38">
-        <v>-3.908669961439836</v>
+        <v>-2.656673812113858</v>
       </c>
       <c r="G38">
-        <v>-9.368580183162651</v>
+        <v>-5.488716816957459</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.573907769142991</v>
       </c>
       <c r="E39">
-        <v>-29.66304650811105</v>
+        <v>-24.96190178652822</v>
       </c>
       <c r="F39">
-        <v>-3.492013583342727</v>
+        <v>-2.917399967042794</v>
       </c>
       <c r="G39">
-        <v>-8.82164164407412</v>
+        <v>-4.682728089420957</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.244438355358008</v>
       </c>
       <c r="E40">
-        <v>-28.08062560781874</v>
+        <v>-24.23773539406563</v>
       </c>
       <c r="F40">
-        <v>-3.772798654930453</v>
+        <v>-2.874710881306925</v>
       </c>
       <c r="G40">
-        <v>-8.957552780643359</v>
+        <v>-6.043786055890441</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.916556493765494</v>
       </c>
       <c r="E41">
-        <v>-27.72663026616514</v>
+        <v>-24.57915516339992</v>
       </c>
       <c r="F41">
-        <v>-3.401089492109245</v>
+        <v>-2.649136497115785</v>
       </c>
       <c r="G41">
-        <v>-8.458885306062941</v>
+        <v>-5.018261811462709</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.591069214091359</v>
       </c>
       <c r="E42">
-        <v>-29.12890847043233</v>
+        <v>-23.46128776918447</v>
       </c>
       <c r="F42">
-        <v>-3.619263241923773</v>
+        <v>-2.802646230732979</v>
       </c>
       <c r="G42">
-        <v>-7.170871216371935</v>
+        <v>-5.113658491722348</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.279517799128175</v>
       </c>
       <c r="E43">
-        <v>-27.98395174470299</v>
+        <v>-23.07331981552533</v>
       </c>
       <c r="F43">
-        <v>-3.907989043434736</v>
+        <v>-2.602733011945763</v>
       </c>
       <c r="G43">
-        <v>-9.021479415006686</v>
+        <v>-4.752901723216888</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.983580599872369</v>
       </c>
       <c r="E44">
-        <v>-29.23967041618593</v>
+        <v>-22.99387679600877</v>
       </c>
       <c r="F44">
-        <v>-3.735643063445284</v>
+        <v>-2.676492502225837</v>
       </c>
       <c r="G44">
-        <v>-8.300575018374992</v>
+        <v>-5.36538575343745</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.712890040801684</v>
       </c>
       <c r="E45">
-        <v>-25.86831208695551</v>
+        <v>-22.93564062027013</v>
       </c>
       <c r="F45">
-        <v>-3.3091407103985</v>
+        <v>-2.996709518921624</v>
       </c>
       <c r="G45">
-        <v>-8.450244782205441</v>
+        <v>-4.374559336806819</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.475951079766165</v>
       </c>
       <c r="E46">
-        <v>-25.99615996514006</v>
+        <v>-21.34131889028566</v>
       </c>
       <c r="F46">
-        <v>-3.560419335098508</v>
+        <v>-2.8568313992849</v>
       </c>
       <c r="G46">
-        <v>-7.991548834466183</v>
+        <v>-4.361105279735222</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.274629744370125</v>
       </c>
       <c r="E47">
-        <v>-25.62585758858484</v>
+        <v>-21.7353685845371</v>
       </c>
       <c r="F47">
-        <v>-3.449388281896873</v>
+        <v>-2.742009736848055</v>
       </c>
       <c r="G47">
-        <v>-7.938831707298829</v>
+        <v>-4.776035815445315</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.118649153558736</v>
       </c>
       <c r="E48">
-        <v>-25.44990825949081</v>
+        <v>-21.48154308793317</v>
       </c>
       <c r="F48">
-        <v>-3.77449597973879</v>
+        <v>-2.852426141436812</v>
       </c>
       <c r="G48">
-        <v>-9.048807968433369</v>
+        <v>-4.834006778383493</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.008449972057269</v>
       </c>
       <c r="E49">
-        <v>-25.35147281998608</v>
+        <v>-21.05917231723776</v>
       </c>
       <c r="F49">
-        <v>-3.68618538766114</v>
+        <v>-2.873563592454047</v>
       </c>
       <c r="G49">
-        <v>-8.005290908999697</v>
+        <v>-5.01448778954794</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.943475190402922</v>
       </c>
       <c r="E50">
-        <v>-24.08270761488704</v>
+        <v>-20.3228696144346</v>
       </c>
       <c r="F50">
-        <v>-3.233043567307726</v>
+        <v>-3.01015972044088</v>
       </c>
       <c r="G50">
-        <v>-8.316094855863096</v>
+        <v>-4.804003304161078</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.92629445312158</v>
       </c>
       <c r="E51">
-        <v>-23.96759833408607</v>
+        <v>-19.32279688610667</v>
       </c>
       <c r="F51">
-        <v>-3.728592828480058</v>
+        <v>-2.767675044088992</v>
       </c>
       <c r="G51">
-        <v>-8.113966187417354</v>
+        <v>-5.140636127321868</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.948928449127614</v>
       </c>
       <c r="E52">
-        <v>-23.70570309680047</v>
+        <v>-19.24485731996066</v>
       </c>
       <c r="F52">
-        <v>-3.038293562542159</v>
+        <v>-2.770986856965384</v>
       </c>
       <c r="G52">
-        <v>-7.755103050960357</v>
+        <v>-5.351021296342553</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.009658303014015</v>
       </c>
       <c r="E53">
-        <v>-22.91134082874497</v>
+        <v>-19.11107714082606</v>
       </c>
       <c r="F53">
-        <v>-3.676542362725151</v>
+        <v>-3.048210777088475</v>
       </c>
       <c r="G53">
-        <v>-9.506255840504322</v>
+        <v>-5.46432140687857</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.101009710827283</v>
       </c>
       <c r="E54">
-        <v>-22.17433168399662</v>
+        <v>-18.12673180272677</v>
       </c>
       <c r="F54">
-        <v>-3.660133232843095</v>
+        <v>-2.890437436449073</v>
       </c>
       <c r="G54">
-        <v>-8.418387402481036</v>
+        <v>-5.690358835208928</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.211440863262975</v>
       </c>
       <c r="E55">
-        <v>-22.39411664148489</v>
+        <v>-18.49230645241798</v>
       </c>
       <c r="F55">
-        <v>-3.56561899728588</v>
+        <v>-2.930686151816296</v>
       </c>
       <c r="G55">
-        <v>-9.490659860468815</v>
+        <v>-5.591946247963014</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.334972249766508</v>
       </c>
       <c r="E56">
-        <v>-22.3586405761088</v>
+        <v>-17.45468361761845</v>
       </c>
       <c r="F56">
-        <v>-2.939896768968023</v>
+        <v>-2.848420156676874</v>
       </c>
       <c r="G56">
-        <v>-9.008846373228826</v>
+        <v>-5.417440771496951</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.457048554420664</v>
       </c>
       <c r="E57">
-        <v>-22.18922130653384</v>
+        <v>-17.87797366853742</v>
       </c>
       <c r="F57">
-        <v>-3.402003181354533</v>
+        <v>-2.816274531243836</v>
       </c>
       <c r="G57">
-        <v>-8.993485441926609</v>
+        <v>-5.609833125511695</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.568694396536293</v>
       </c>
       <c r="E58">
-        <v>-20.37200355741782</v>
+        <v>-17.43313713828995</v>
       </c>
       <c r="F58">
-        <v>-3.486432043782664</v>
+        <v>-2.898888440692434</v>
       </c>
       <c r="G58">
-        <v>-9.507424463079685</v>
+        <v>-5.570090026312745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.661556747904709</v>
       </c>
       <c r="E59">
-        <v>-20.3139530491135</v>
+        <v>-16.81941569840043</v>
       </c>
       <c r="F59">
-        <v>-3.383789038901778</v>
+        <v>-2.864747278186052</v>
       </c>
       <c r="G59">
-        <v>-10.46108669548646</v>
+        <v>-6.135607346967667</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.725100376541658</v>
       </c>
       <c r="E60">
-        <v>-21.59628556233952</v>
+        <v>-17.24850672452323</v>
       </c>
       <c r="F60">
-        <v>-3.778215349377359</v>
+        <v>-2.443012179542379</v>
       </c>
       <c r="G60">
-        <v>-9.899565203297437</v>
+        <v>-6.183130228183905</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.757387665463378</v>
       </c>
       <c r="E61">
-        <v>-19.86929312935233</v>
+        <v>-16.0188901772205</v>
       </c>
       <c r="F61">
-        <v>-3.628137541909965</v>
+        <v>-2.655970528188881</v>
       </c>
       <c r="G61">
-        <v>-9.648900626700438</v>
+        <v>-6.221363718616947</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.754005306292456</v>
       </c>
       <c r="E62">
-        <v>-20.5144467073291</v>
+        <v>-16.86740393745971</v>
       </c>
       <c r="F62">
-        <v>-3.334017411871972</v>
+        <v>-2.655246535078835</v>
       </c>
       <c r="G62">
-        <v>-10.46777399747578</v>
+        <v>-5.87504423920825</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.714279422306992</v>
       </c>
       <c r="E63">
-        <v>-20.70524490269427</v>
+        <v>-16.78548384266096</v>
       </c>
       <c r="F63">
-        <v>-3.342649000209143</v>
+        <v>-2.872842084446209</v>
       </c>
       <c r="G63">
-        <v>-9.922235819150364</v>
+        <v>-7.050079341280547</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.643151927750835</v>
       </c>
       <c r="E64">
-        <v>-21.13861533675432</v>
+        <v>-16.43424634167803</v>
       </c>
       <c r="F64">
-        <v>-3.204734111317053</v>
+        <v>-2.737106630190885</v>
       </c>
       <c r="G64">
-        <v>-10.45484300659939</v>
+        <v>-6.335332559351897</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.541198546589482</v>
       </c>
       <c r="E65">
-        <v>-19.25564414504693</v>
+        <v>-15.52405929392835</v>
       </c>
       <c r="F65">
-        <v>-3.481734372241388</v>
+        <v>-2.905772173809698</v>
       </c>
       <c r="G65">
-        <v>-10.93566001963206</v>
+        <v>-6.573771291272366</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.416112633781749</v>
       </c>
       <c r="E66">
-        <v>-19.95028035850551</v>
+        <v>-15.82935995457747</v>
       </c>
       <c r="F66">
-        <v>-3.59543359684744</v>
+        <v>-2.643932693091399</v>
       </c>
       <c r="G66">
-        <v>-9.748226924515192</v>
+        <v>-7.012726455960951</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.274038250475118</v>
       </c>
       <c r="E67">
-        <v>-20.69911334888788</v>
+        <v>-15.76249703585421</v>
       </c>
       <c r="F67">
-        <v>-3.532299575243075</v>
+        <v>-2.968024812497483</v>
       </c>
       <c r="G67">
-        <v>-10.29710875383528</v>
+        <v>-6.62403861474066</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.120931219880911</v>
       </c>
       <c r="E68">
-        <v>-20.31177938158982</v>
+        <v>-15.17974130122914</v>
       </c>
       <c r="F68">
-        <v>-3.449537388029377</v>
+        <v>-2.857853604659955</v>
       </c>
       <c r="G68">
-        <v>-10.52770149282767</v>
+        <v>-7.254012257045192</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.969632016619483</v>
       </c>
       <c r="E69">
-        <v>-18.94053480969719</v>
+        <v>-16.17265904062495</v>
       </c>
       <c r="F69">
-        <v>-3.155284719206937</v>
+        <v>-2.797174035670085</v>
       </c>
       <c r="G69">
-        <v>-10.27490492490339</v>
+        <v>-6.756424020310575</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.826729593931805</v>
       </c>
       <c r="E70">
-        <v>-20.20542816951968</v>
+        <v>-14.92169979532407</v>
       </c>
       <c r="F70">
-        <v>-3.402711435483927</v>
+        <v>-2.921309861184008</v>
       </c>
       <c r="G70">
-        <v>-9.904484673968792</v>
+        <v>-6.923494011495435</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.70490112340171</v>
       </c>
       <c r="E71">
-        <v>-19.11183339598534</v>
+        <v>-15.85452015616408</v>
       </c>
       <c r="F71">
-        <v>-3.866259207151308</v>
+        <v>-2.912804184692062</v>
       </c>
       <c r="G71">
-        <v>-10.48210534911529</v>
+        <v>-6.509103094708243</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.614388680945303</v>
       </c>
       <c r="E72">
-        <v>-19.88942219631642</v>
+        <v>-16.0248541774886</v>
       </c>
       <c r="F72">
-        <v>-3.781270368358884</v>
+        <v>-2.946448326756764</v>
       </c>
       <c r="G72">
-        <v>-10.94251946998943</v>
+        <v>-7.1892877812069</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.558504564995866</v>
       </c>
       <c r="E73">
-        <v>-19.60258412419658</v>
+        <v>-16.32879176746141</v>
       </c>
       <c r="F73">
-        <v>-3.900736686823226</v>
+        <v>-2.964840568201122</v>
       </c>
       <c r="G73">
-        <v>-10.99916290416636</v>
+        <v>-7.331598202303551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.543574307220299</v>
       </c>
       <c r="E74">
-        <v>-18.83349526957789</v>
+        <v>-15.39857075070179</v>
       </c>
       <c r="F74">
-        <v>-4.022886915672638</v>
+        <v>-3.095590079058996</v>
       </c>
       <c r="G74">
-        <v>-10.57442653256895</v>
+        <v>-7.207055479116169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.56531826099672</v>
       </c>
       <c r="E75">
-        <v>-20.11882563259699</v>
+        <v>-15.40707975336221</v>
       </c>
       <c r="F75">
-        <v>-3.555165829029953</v>
+        <v>-3.069976958964435</v>
       </c>
       <c r="G75">
-        <v>-9.839776750858197</v>
+        <v>-7.074084106985802</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.618419649301298</v>
       </c>
       <c r="E76">
-        <v>-20.74197082689648</v>
+        <v>-16.10984457766455</v>
       </c>
       <c r="F76">
-        <v>-4.039552839449561</v>
+        <v>-3.018845981026636</v>
       </c>
       <c r="G76">
-        <v>-10.02495211559733</v>
+        <v>-6.553868291490267</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.698874347701174</v>
       </c>
       <c r="E77">
-        <v>-20.57480220890332</v>
+        <v>-16.5985937203644</v>
       </c>
       <c r="F77">
-        <v>-4.108128406522916</v>
+        <v>-3.245183291595753</v>
       </c>
       <c r="G77">
-        <v>-10.3644915977416</v>
+        <v>-6.907067084529571</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.795595211619305</v>
       </c>
       <c r="E78">
-        <v>-21.92937293949971</v>
+        <v>-17.54662522539618</v>
       </c>
       <c r="F78">
-        <v>-3.453001620507885</v>
+        <v>-3.186601977237175</v>
       </c>
       <c r="G78">
-        <v>-9.444639966927408</v>
+        <v>-6.338580204525923</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.904867665911155</v>
       </c>
       <c r="E79">
-        <v>-22.13785482586484</v>
+        <v>-17.87446410118148</v>
       </c>
       <c r="F79">
-        <v>-3.790398148770332</v>
+        <v>-3.350388436853498</v>
       </c>
       <c r="G79">
-        <v>-9.801215516416768</v>
+        <v>-6.6669168005653</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.02154134829846</v>
       </c>
       <c r="E80">
-        <v>-21.94919407023128</v>
+        <v>-18.15525213202708</v>
       </c>
       <c r="F80">
-        <v>-4.414542337185855</v>
+        <v>-3.487213194243504</v>
       </c>
       <c r="G80">
-        <v>-8.803592549794013</v>
+        <v>-6.754543630444269</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.140371144930265</v>
       </c>
       <c r="E81">
-        <v>-22.20795107502956</v>
+        <v>-18.67265745824746</v>
       </c>
       <c r="F81">
-        <v>-3.853735948755785</v>
+        <v>-3.703685477412682</v>
       </c>
       <c r="G81">
-        <v>-11.09526473062586</v>
+        <v>-6.883985961029772</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.26704148204496</v>
       </c>
       <c r="E82">
-        <v>-22.41679976778931</v>
+        <v>-18.95997102013812</v>
       </c>
       <c r="F82">
-        <v>-4.301051032797907</v>
+        <v>-3.633944397403589</v>
       </c>
       <c r="G82">
-        <v>-10.22708409458861</v>
+        <v>-6.539871304950228</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.401528287783666</v>
       </c>
       <c r="E83">
-        <v>-24.7585597181618</v>
+        <v>-19.64241205309404</v>
       </c>
       <c r="F83">
-        <v>-4.199061609797829</v>
+        <v>-3.626453470980073</v>
       </c>
       <c r="G83">
-        <v>-10.31387666699169</v>
+        <v>-7.053737494101441</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.55260676244919</v>
       </c>
       <c r="E84">
-        <v>-24.62741058242566</v>
+        <v>-20.97830282840878</v>
       </c>
       <c r="F84">
-        <v>-4.726110369829014</v>
+        <v>-3.941815426328053</v>
       </c>
       <c r="G84">
-        <v>-10.50293199110284</v>
+        <v>-6.278765267722371</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.731647655519468</v>
       </c>
       <c r="E85">
-        <v>-25.29877949643283</v>
+        <v>-21.83539351841852</v>
       </c>
       <c r="F85">
-        <v>-4.148827753757261</v>
+        <v>-3.816171972141035</v>
       </c>
       <c r="G85">
-        <v>-9.848824471817027</v>
+        <v>-6.4357083001026</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.944045862949307</v>
       </c>
       <c r="E86">
-        <v>-26.34745180781108</v>
+        <v>-22.46544916405372</v>
       </c>
       <c r="F86">
-        <v>-4.732483000258751</v>
+        <v>-3.817661376731269</v>
       </c>
       <c r="G86">
-        <v>-8.831129667589671</v>
+        <v>-6.623979024920953</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.20609884293235</v>
       </c>
       <c r="E87">
-        <v>-26.90019734518732</v>
+        <v>-23.31961898832851</v>
       </c>
       <c r="F87">
-        <v>-4.860996747496468</v>
+        <v>-3.853638201402254</v>
       </c>
       <c r="G87">
-        <v>-10.06475811516153</v>
+        <v>-5.237856918173645</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.524819791485817</v>
       </c>
       <c r="E88">
-        <v>-26.51008289484854</v>
+        <v>-25.24333738915692</v>
       </c>
       <c r="F88">
-        <v>-4.899468614784686</v>
+        <v>-4.022418059722654</v>
       </c>
       <c r="G88">
-        <v>-10.41014402072815</v>
+        <v>-5.992747375311497</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.906801782055042</v>
       </c>
       <c r="E89">
-        <v>-29.73051397811433</v>
+        <v>-26.12560639464931</v>
       </c>
       <c r="F89">
-        <v>-4.73229661759312</v>
+        <v>-4.257299980051648</v>
       </c>
       <c r="G89">
-        <v>-9.56531928347046</v>
+        <v>-6.698760938107549</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.363655770744355</v>
       </c>
       <c r="E90">
-        <v>-29.8205287202018</v>
+        <v>-27.37940499315301</v>
       </c>
       <c r="F90">
-        <v>-4.823895828259884</v>
+        <v>-4.45066992472415</v>
       </c>
       <c r="G90">
-        <v>-9.902478483371995</v>
+        <v>-5.66300710796347</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.889887617700897</v>
       </c>
       <c r="E91">
-        <v>-31.2536322470392</v>
+        <v>-29.14550532767044</v>
       </c>
       <c r="F91">
-        <v>-4.755519897730605</v>
+        <v>-4.496168832690316</v>
       </c>
       <c r="G91">
-        <v>-9.725741699212463</v>
+        <v>-5.561667998460839</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.48660899037169</v>
       </c>
       <c r="E92">
-        <v>-32.88071748646916</v>
+        <v>-30.21667056944478</v>
       </c>
       <c r="F92">
-        <v>-4.75291136877919</v>
+        <v>-4.690937061538744</v>
       </c>
       <c r="G92">
-        <v>-10.18399072330392</v>
+        <v>-6.166749648855591</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.144479022586712</v>
       </c>
       <c r="E93">
-        <v>-34.21921213433831</v>
+        <v>-32.77634521754037</v>
       </c>
       <c r="F93">
-        <v>-5.149348126941366</v>
+        <v>-4.843717003474071</v>
       </c>
       <c r="G93">
-        <v>-9.510675418799249</v>
+        <v>-5.993373068418419</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.843119447688148</v>
       </c>
       <c r="E94">
-        <v>-36.5783885957443</v>
+        <v>-33.77543526700864</v>
       </c>
       <c r="F94">
-        <v>-5.225357463087442</v>
+        <v>-4.710214827736694</v>
       </c>
       <c r="G94">
-        <v>-10.76847415935333</v>
+        <v>-6.262050323294591</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.574262986822729</v>
       </c>
       <c r="E95">
-        <v>-36.37047503286713</v>
+        <v>-36.96958535137091</v>
       </c>
       <c r="F95">
-        <v>-5.424418291817178</v>
+        <v>-4.990855763396334</v>
       </c>
       <c r="G95">
-        <v>-9.138490647092226</v>
+        <v>-6.399424720992188</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.315929609865</v>
       </c>
       <c r="E96">
-        <v>-40.05515847868828</v>
+        <v>-38.08672818974514</v>
       </c>
       <c r="F96">
-        <v>-5.636395025091363</v>
+        <v>-5.248844164059017</v>
       </c>
       <c r="G96">
-        <v>-9.673928350977329</v>
+        <v>-7.069773776693672</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.04700620211942</v>
       </c>
       <c r="E97">
-        <v>-40.84185177601178</v>
+        <v>-40.14955678361517</v>
       </c>
       <c r="F97">
-        <v>-5.150839188266405</v>
+        <v>-5.189567021082087</v>
       </c>
       <c r="G97">
-        <v>-10.0230187570024</v>
+        <v>-7.116260457156117</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.76493984932568</v>
       </c>
       <c r="E98">
-        <v>-42.83777216641848</v>
+        <v>-42.73815253096075</v>
       </c>
       <c r="F98">
-        <v>-5.875883496547325</v>
+        <v>-5.315298282213801</v>
       </c>
       <c r="G98">
-        <v>-11.35987663557981</v>
+        <v>-8.063857770134945</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.43043236096449</v>
       </c>
       <c r="E99">
-        <v>-45.97541142363904</v>
+        <v>-45.3577864391549</v>
       </c>
       <c r="F99">
-        <v>-6.034973941357179</v>
+        <v>-5.550031096410292</v>
       </c>
       <c r="G99">
-        <v>-11.39695143507411</v>
+        <v>-7.53801071667711</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.07010855275358</v>
       </c>
       <c r="E100">
-        <v>-47.11677254100628</v>
+        <v>-47.39346456711194</v>
       </c>
       <c r="F100">
-        <v>-6.723121522966305</v>
+        <v>-5.835937135282125</v>
       </c>
       <c r="G100">
-        <v>-11.89708548132842</v>
+        <v>-8.236158423271853</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.62506211663651</v>
       </c>
       <c r="E101">
-        <v>-48.76282076534337</v>
+        <v>-49.67296366047147</v>
       </c>
       <c r="F101">
-        <v>-6.444380033761285</v>
+        <v>-6.043093598639419</v>
       </c>
       <c r="G101">
-        <v>-11.84217015192299</v>
+        <v>-8.09109031774099</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.16586448498781</v>
       </c>
       <c r="E102">
-        <v>-50.99058430740227</v>
+        <v>-51.41628463861182</v>
       </c>
       <c r="F102">
-        <v>-6.560532054247026</v>
+        <v>-6.104177410921855</v>
       </c>
       <c r="G102">
-        <v>-11.69315918665486</v>
+        <v>-8.259477906050479</v>
       </c>
     </row>
   </sheetData>
